--- a/s2-charts-exploration/solution.xlsx
+++ b/s2-charts-exploration/solution.xlsx
@@ -560,7 +560,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Part 2: Charts Excel doesn't have</t>
+          <t>Part 2: Five charts, one line each</t>
         </is>
       </c>
     </row>
